--- a/MAJSushiConfig/ig/FRSectionSupportingInformationLMCDAFHIR.xlsx
+++ b/MAJSushiConfig/ig/FRSectionSupportingInformationLMCDAFHIR.xlsx
@@ -26,7 +26,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/ConceptMap/FRSectionSupportingInformationLMCDAFHIR</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/ConceptMap/FRSectionSupportingInformationLMCDAFHIR</t>
   </si>
   <si>
     <t>Version</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:25:17+00:00</t>
+    <t>2026-09-07T11:26:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -107,7 +107,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMSupportingInformation</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMSupportingInformation|0.1.0</t>
   </si>
   <si>
     <t/>

--- a/MAJSushiConfig/ig/FRSectionSupportingInformationLMCDAFHIR.xlsx
+++ b/MAJSushiConfig/ig/FRSectionSupportingInformationLMCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T11:26:50+00:00</t>
+    <t>2026-09-07T11:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
